--- a/research/traditional_assets/database/data/malta/malta_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08689999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0788</v>
+        <v>0.256</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.007314309065206024</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.004626659028304831</v>
       </c>
       <c r="K2">
-        <v>8.029999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="L2">
-        <v>0.1119944211994421</v>
+        <v>0.20703125</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>0.914</v>
       </c>
       <c r="N2">
-        <v>0.01032388663967611</v>
+        <v>0.008943248532289628</v>
       </c>
       <c r="O2">
-        <v>0.1270236612702366</v>
+        <v>0.05748427672955975</v>
       </c>
       <c r="P2">
-        <v>1.02</v>
+        <v>0.914</v>
       </c>
       <c r="Q2">
-        <v>0.01032388663967611</v>
+        <v>0.008943248532289628</v>
       </c>
       <c r="R2">
-        <v>0.1270236612702366</v>
+        <v>0.05748427672955975</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -642,55 +642,61 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.05926199261992619</v>
+        <v>0.1013384321223709</v>
       </c>
       <c r="X2">
-        <v>0.0476292050044209</v>
+        <v>0.06562532251415561</v>
       </c>
       <c r="Y2">
-        <v>0.0116327876155053</v>
+        <v>0.03571310960821533</v>
       </c>
       <c r="Z2">
-        <v>0.5022415242364808</v>
+        <v>0.4839127207053984</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.002238899158163185</v>
       </c>
       <c r="AB2">
-        <v>0.04730701241993947</v>
+        <v>0.06544955239662613</v>
       </c>
       <c r="AC2">
-        <v>-0.04730701241993947</v>
+        <v>-0.06321065323846295</v>
       </c>
       <c r="AD2">
-        <v>1.16</v>
+        <v>0.23</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.6463053189608865</v>
       </c>
       <c r="AF2">
-        <v>1.16</v>
+        <v>0.8763053189608865</v>
       </c>
       <c r="AG2">
-        <v>1.16</v>
+        <v>0.8763053189608865</v>
       </c>
       <c r="AH2">
-        <v>0.0116046418567427</v>
+        <v>0.008501520463400719</v>
       </c>
       <c r="AI2">
-        <v>0.00692289329195512</v>
+        <v>0.005750929037992916</v>
       </c>
       <c r="AJ2">
-        <v>0.0116046418567427</v>
+        <v>0.008501520463400719</v>
       </c>
       <c r="AK2">
-        <v>0.00692289329195512</v>
+        <v>0.005750929037992916</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0.3328509406657019</v>
+      </c>
+      <c r="AP2">
+        <v>1.268169781419517</v>
       </c>
     </row>
     <row r="3">
@@ -710,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08689999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0788</v>
+        <v>0.256</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,34 +728,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.007314309065206024</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.004626659028304831</v>
       </c>
       <c r="K3">
-        <v>8.029999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="L3">
-        <v>0.1119944211994421</v>
+        <v>0.20703125</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>0.914</v>
       </c>
       <c r="N3">
-        <v>0.01032388663967611</v>
+        <v>0.008943248532289628</v>
       </c>
       <c r="O3">
-        <v>0.1270236612702366</v>
+        <v>0.05748427672955975</v>
       </c>
       <c r="P3">
-        <v>1.02</v>
+        <v>0.914</v>
       </c>
       <c r="Q3">
-        <v>0.01032388663967611</v>
+        <v>0.008943248532289628</v>
       </c>
       <c r="R3">
-        <v>0.1270236612702366</v>
+        <v>0.05748427672955975</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +770,61 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.05926199261992619</v>
+        <v>0.1013384321223709</v>
       </c>
       <c r="X3">
-        <v>0.0476292050044209</v>
+        <v>0.06562532251415561</v>
       </c>
       <c r="Y3">
-        <v>0.0116327876155053</v>
+        <v>0.03571310960821533</v>
       </c>
       <c r="Z3">
-        <v>0.5022415242364808</v>
+        <v>0.4839127207053984</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.002238899158163185</v>
       </c>
       <c r="AB3">
-        <v>0.04730701241993947</v>
+        <v>0.06544955239662613</v>
       </c>
       <c r="AC3">
-        <v>-0.04730701241993947</v>
+        <v>-0.06321065323846295</v>
       </c>
       <c r="AD3">
-        <v>1.16</v>
+        <v>0.23</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.6463053189608865</v>
       </c>
       <c r="AF3">
-        <v>1.16</v>
+        <v>0.8763053189608865</v>
       </c>
       <c r="AG3">
-        <v>1.16</v>
+        <v>0.8763053189608865</v>
       </c>
       <c r="AH3">
-        <v>0.0116046418567427</v>
+        <v>0.008501520463400719</v>
       </c>
       <c r="AI3">
-        <v>0.00692289329195512</v>
+        <v>0.005750929037992916</v>
       </c>
       <c r="AJ3">
-        <v>0.0116046418567427</v>
+        <v>0.008501520463400719</v>
       </c>
       <c r="AK3">
-        <v>0.00692289329195512</v>
+        <v>0.005750929037992916</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0.3328509406657019</v>
+      </c>
+      <c r="AP3">
+        <v>1.268169781419517</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malta/malta_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08169999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="E2">
-        <v>0.256</v>
+        <v>0.279</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.007314309065206024</v>
+        <v>0.005762371928723246</v>
       </c>
       <c r="J2">
-        <v>0.004626659028304831</v>
+        <v>0.003679352346380722</v>
       </c>
       <c r="K2">
-        <v>15.9</v>
+        <v>18.7</v>
       </c>
       <c r="L2">
-        <v>0.20703125</v>
+        <v>0.2305795314426634</v>
       </c>
       <c r="M2">
-        <v>0.914</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="N2">
-        <v>0.008943248532289628</v>
+        <v>0.01005387931034483</v>
       </c>
       <c r="O2">
-        <v>0.05748427672955975</v>
+        <v>0.04989304812834225</v>
       </c>
       <c r="P2">
-        <v>0.914</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.008943248532289628</v>
+        <v>0.01005387931034483</v>
       </c>
       <c r="R2">
-        <v>0.05748427672955975</v>
+        <v>0.04989304812834225</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>32.1</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.3459051724137931</v>
       </c>
       <c r="W2">
-        <v>0.1013384321223709</v>
+        <v>0.119795003203075</v>
       </c>
       <c r="X2">
-        <v>0.06562532251415561</v>
+        <v>0.05655740482452965</v>
       </c>
       <c r="Y2">
-        <v>0.03571310960821533</v>
+        <v>0.06323759837854531</v>
       </c>
       <c r="Z2">
-        <v>0.4839127207053984</v>
+        <v>0.6507869400828512</v>
       </c>
       <c r="AA2">
-        <v>0.002238899158163185</v>
+        <v>0.002394474454987769</v>
       </c>
       <c r="AB2">
-        <v>0.06544955239662613</v>
+        <v>0.05555870696969224</v>
       </c>
       <c r="AC2">
-        <v>-0.06321065323846295</v>
+        <v>-0.05316423251470447</v>
       </c>
       <c r="AD2">
-        <v>0.23</v>
+        <v>5.07</v>
       </c>
       <c r="AE2">
-        <v>0.6463053189608865</v>
+        <v>0.5433581829027234</v>
       </c>
       <c r="AF2">
-        <v>0.8763053189608865</v>
+        <v>5.613358182902724</v>
       </c>
       <c r="AG2">
-        <v>0.8763053189608865</v>
+        <v>-26.48664181709728</v>
       </c>
       <c r="AH2">
-        <v>0.008501520463400719</v>
+        <v>0.05703857978781917</v>
       </c>
       <c r="AI2">
-        <v>0.005750929037992916</v>
+        <v>0.03512446172664969</v>
       </c>
       <c r="AJ2">
-        <v>0.008501520463400719</v>
+        <v>-0.3994163852182382</v>
       </c>
       <c r="AK2">
-        <v>0.005750929037992916</v>
+        <v>-0.2073913190753691</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.3328509406657019</v>
+        <v>8.802083333333334</v>
       </c>
       <c r="AP2">
-        <v>1.268169781419517</v>
+        <v>-45.98375315468278</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08169999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="E3">
-        <v>0.256</v>
+        <v>0.279</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +728,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.007314309065206024</v>
+        <v>0.005762371928723246</v>
       </c>
       <c r="J3">
-        <v>0.004626659028304831</v>
+        <v>0.003679352346380722</v>
       </c>
       <c r="K3">
-        <v>15.9</v>
+        <v>18.7</v>
       </c>
       <c r="L3">
-        <v>0.20703125</v>
+        <v>0.2305795314426634</v>
       </c>
       <c r="M3">
-        <v>0.914</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="N3">
-        <v>0.008943248532289628</v>
+        <v>0.01005387931034483</v>
       </c>
       <c r="O3">
-        <v>0.05748427672955975</v>
+        <v>0.04989304812834225</v>
       </c>
       <c r="P3">
-        <v>0.914</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.008943248532289628</v>
+        <v>0.01005387931034483</v>
       </c>
       <c r="R3">
-        <v>0.05748427672955975</v>
+        <v>0.04989304812834225</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>32.1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.3459051724137931</v>
       </c>
       <c r="W3">
-        <v>0.1013384321223709</v>
+        <v>0.119795003203075</v>
       </c>
       <c r="X3">
-        <v>0.06562532251415561</v>
+        <v>0.05655740482452965</v>
       </c>
       <c r="Y3">
-        <v>0.03571310960821533</v>
+        <v>0.06323759837854531</v>
       </c>
       <c r="Z3">
-        <v>0.4839127207053984</v>
+        <v>0.6507869400828512</v>
       </c>
       <c r="AA3">
-        <v>0.002238899158163185</v>
+        <v>0.002394474454987769</v>
       </c>
       <c r="AB3">
-        <v>0.06544955239662613</v>
+        <v>0.05555870696969224</v>
       </c>
       <c r="AC3">
-        <v>-0.06321065323846295</v>
+        <v>-0.05316423251470447</v>
       </c>
       <c r="AD3">
-        <v>0.23</v>
+        <v>5.07</v>
       </c>
       <c r="AE3">
-        <v>0.6463053189608865</v>
+        <v>0.5433581829027234</v>
       </c>
       <c r="AF3">
-        <v>0.8763053189608865</v>
+        <v>5.613358182902724</v>
       </c>
       <c r="AG3">
-        <v>0.8763053189608865</v>
+        <v>-26.48664181709728</v>
       </c>
       <c r="AH3">
-        <v>0.008501520463400719</v>
+        <v>0.05703857978781917</v>
       </c>
       <c r="AI3">
-        <v>0.005750929037992916</v>
+        <v>0.03512446172664969</v>
       </c>
       <c r="AJ3">
-        <v>0.008501520463400719</v>
+        <v>-0.3994163852182382</v>
       </c>
       <c r="AK3">
-        <v>0.005750929037992916</v>
+        <v>-0.2073913190753691</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.3328509406657019</v>
+        <v>8.802083333333334</v>
       </c>
       <c r="AP3">
-        <v>1.268169781419517</v>
+        <v>-45.98375315468278</v>
       </c>
     </row>
   </sheetData>
